--- a/templates/template_correc_excava.xlsx
+++ b/templates/template_correc_excava.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\EquiposUnidos\app\src\main\res\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E67123-8EB8-40BF-992E-9FD7B21A49F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06C58AB-4DA4-4713-89A1-56E6B9EDF013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FT-MANT-11" sheetId="15" r:id="rId1"/>
@@ -31,15 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>Código</t>
   </si>
   <si>
     <t>Fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Observaciones:</t>
@@ -1214,43 +1211,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1363,6 +1323,43 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1428,7 +1425,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1456,9 +1453,6 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -1471,21 +1465,15 @@
     <xf numFmtId="0" fontId="24" fillId="25" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1508,15 +1496,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1696,7 +1675,7 @@
     <xf numFmtId="0" fontId="24" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1768,13 +1747,13 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1783,13 +1762,13 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1800,6 +1779,15 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="60">
@@ -2645,909 +2633,907 @@
   <dimension ref="B1:G95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="49.109375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="10"/>
+    <col min="1" max="1" width="6.88671875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="49.109375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B1" s="43"/>
-      <c r="C1" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="47"/>
-      <c r="E1" s="48"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
+      <c r="B2" s="38"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B2" s="44"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B3" s="45"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
       <c r="F3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>45154</v>
       </c>
     </row>
     <row r="4" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="57"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
     </row>
     <row r="5" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="58" t="s">
-        <v>6</v>
+      <c r="E5" s="62"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="52" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="58"/>
+      <c r="D6" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="62"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B7" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="73"/>
+      <c r="D7" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="62"/>
+      <c r="F7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="76" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="74"/>
+      <c r="D8" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="71"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="B9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="69"/>
+    </row>
+    <row r="10" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
+      <c r="B10" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="74"/>
+    </row>
+    <row r="11" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B11" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B12" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B13" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1" thickBot="1">
+      <c r="B14" s="75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="76"/>
+      <c r="D14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="54"/>
+      <c r="G14" s="55"/>
+    </row>
+    <row r="15" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+    </row>
+    <row r="16" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="33"/>
+    </row>
+    <row r="17" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
+    </row>
+    <row r="18" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
+    </row>
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="36"/>
+    </row>
+    <row r="20" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B20" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="30"/>
+    </row>
+    <row r="21" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
+    </row>
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="114"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="33"/>
+    </row>
+    <row r="23" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B23" s="20"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="33"/>
+    </row>
+    <row r="24" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+    </row>
+    <row r="25" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B25" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
+    </row>
+    <row r="26" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="114"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="33"/>
+    </row>
+    <row r="27" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="33"/>
+    </row>
+    <row r="28" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="33"/>
+    </row>
+    <row r="29" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B30" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="33"/>
+    </row>
+    <row r="32" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="33"/>
+    </row>
+    <row r="33" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="33"/>
+    </row>
+    <row r="34" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="36"/>
+    </row>
+    <row r="35" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B35" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="30"/>
+    </row>
+    <row r="36" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="33"/>
+    </row>
+    <row r="37" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="33"/>
+    </row>
+    <row r="38" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="33"/>
+    </row>
+    <row r="39" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B39" s="20"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="115"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="36"/>
+    </row>
+    <row r="40" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B40" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="30"/>
+    </row>
+    <row r="41" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="114"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="33"/>
+    </row>
+    <row r="42" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="114"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="33"/>
+    </row>
+    <row r="43" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="33"/>
+    </row>
+    <row r="44" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B44" s="20"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="115"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="36"/>
+    </row>
+    <row r="45" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B45" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" s="113"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="30"/>
+    </row>
+    <row r="46" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="33"/>
+    </row>
+    <row r="47" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="33"/>
+    </row>
+    <row r="48" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="33"/>
+    </row>
+    <row r="49" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="115"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="36"/>
+    </row>
+    <row r="50" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B50" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="30"/>
+    </row>
+    <row r="51" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="114"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="33"/>
+    </row>
+    <row r="52" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B52" s="20"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="33"/>
+    </row>
+    <row r="53" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B53" s="20"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="114"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="33"/>
+    </row>
+    <row r="54" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="115"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="36"/>
+    </row>
+    <row r="55" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B55" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="30"/>
+    </row>
+    <row r="56" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B56" s="20"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="114"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="33"/>
+    </row>
+    <row r="57" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B57" s="20"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="33"/>
+    </row>
+    <row r="58" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B58" s="20"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="114"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="33"/>
+    </row>
+    <row r="59" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B59" s="20"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="115"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="36"/>
+    </row>
+    <row r="60" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B60" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="30"/>
+    </row>
+    <row r="61" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="114"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="33"/>
+    </row>
+    <row r="62" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B62" s="20"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="33"/>
+    </row>
+    <row r="63" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B63" s="20"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="114"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="33"/>
+    </row>
+    <row r="64" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="115"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="36"/>
+    </row>
+    <row r="65" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B65" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="25"/>
+      <c r="D65" s="113"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="30"/>
+    </row>
+    <row r="66" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B66" s="26"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="114"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="33"/>
+    </row>
+    <row r="67" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B67" s="26"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="33"/>
+    </row>
+    <row r="68" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B68" s="26"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="114"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="33"/>
+    </row>
+    <row r="69" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B69" s="26"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="115"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="36"/>
+    </row>
+    <row r="70" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B70" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="113"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="30"/>
+    </row>
+    <row r="71" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B71" s="20"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="114"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="33"/>
+    </row>
+    <row r="72" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B72" s="20"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="114"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="33"/>
+    </row>
+    <row r="73" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B73" s="20"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="114"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="33"/>
+    </row>
+    <row r="74" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B74" s="22"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="115"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="36"/>
+    </row>
+    <row r="75" spans="2:7" ht="30" customHeight="1" thickBot="1">
+      <c r="B75" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="75"/>
-    </row>
-    <row r="10" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
-      <c r="B10" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="80"/>
-    </row>
-    <row r="11" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B11" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B12" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B13" s="65" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1" thickBot="1">
-      <c r="B14" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="60"/>
-      <c r="G14" s="61"/>
-    </row>
-    <row r="15" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B15" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-    </row>
-    <row r="16" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="39"/>
-    </row>
-    <row r="17" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="39"/>
-    </row>
-    <row r="18" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
-    </row>
-    <row r="19" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B20" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-    </row>
-    <row r="21" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
-    </row>
-    <row r="22" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
-    </row>
-    <row r="23" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-    </row>
-    <row r="24" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B24" s="23"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
-    </row>
-    <row r="25" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B25" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B26" s="23"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="39"/>
-    </row>
-    <row r="27" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B27" s="23"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="39"/>
-    </row>
-    <row r="28" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B28" s="23"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39"/>
-    </row>
-    <row r="29" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="42"/>
-    </row>
-    <row r="30" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B30" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="36"/>
-    </row>
-    <row r="31" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B31" s="23"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="39"/>
-    </row>
-    <row r="32" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="39"/>
-    </row>
-    <row r="33" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="23"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="39"/>
-    </row>
-    <row r="34" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="42"/>
-    </row>
-    <row r="35" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="36"/>
-    </row>
-    <row r="36" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="39"/>
-    </row>
-    <row r="37" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="39"/>
-    </row>
-    <row r="38" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
-    </row>
-    <row r="39" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="42"/>
-    </row>
-    <row r="40" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B40" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-    </row>
-    <row r="41" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="39"/>
-    </row>
-    <row r="42" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B42" s="23"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="39"/>
-    </row>
-    <row r="43" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B43" s="23"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="39"/>
-    </row>
-    <row r="44" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B44" s="23"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="42"/>
-    </row>
-    <row r="45" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B45" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="36"/>
-    </row>
-    <row r="46" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B46" s="23"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="39"/>
-    </row>
-    <row r="47" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B47" s="23"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="39"/>
-    </row>
-    <row r="48" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B48" s="23"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="39"/>
-    </row>
-    <row r="49" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B49" s="23"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="42"/>
-    </row>
-    <row r="50" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B50" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="36"/>
-    </row>
-    <row r="51" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B51" s="23"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="39"/>
-    </row>
-    <row r="52" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B52" s="23"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="39"/>
-    </row>
-    <row r="53" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B53" s="23"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="39"/>
-    </row>
-    <row r="54" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B54" s="23"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="42"/>
-    </row>
-    <row r="55" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B55" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="36"/>
-    </row>
-    <row r="56" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B56" s="23"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="39"/>
-    </row>
-    <row r="57" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B57" s="23"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="39"/>
-    </row>
-    <row r="58" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B58" s="23"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="39"/>
-    </row>
-    <row r="59" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B59" s="23"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="40"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="42"/>
-    </row>
-    <row r="60" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B60" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" s="22"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="36"/>
-    </row>
-    <row r="61" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B61" s="23"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="39"/>
-    </row>
-    <row r="62" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B62" s="23"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="39"/>
-    </row>
-    <row r="63" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B63" s="23"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="39"/>
-    </row>
-    <row r="64" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B64" s="23"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="40"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="42"/>
-    </row>
-    <row r="65" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B65" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" s="31"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="36"/>
-    </row>
-    <row r="66" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B66" s="32"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="39"/>
-    </row>
-    <row r="67" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B67" s="32"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="39"/>
-    </row>
-    <row r="68" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B68" s="32"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="39"/>
-    </row>
-    <row r="69" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B69" s="32"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="40"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="42"/>
-    </row>
-    <row r="70" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B70" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="22"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="36"/>
-    </row>
-    <row r="71" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B71" s="23"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="39"/>
-    </row>
-    <row r="72" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B72" s="23"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="39"/>
-    </row>
-    <row r="73" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B73" s="23"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="39"/>
-    </row>
-    <row r="74" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B74" s="25"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="42"/>
-    </row>
-    <row r="75" spans="2:7" ht="30" customHeight="1" thickBot="1">
-      <c r="B75" s="83" t="s">
+      <c r="C75" s="77"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="78"/>
+    </row>
+    <row r="76" spans="2:7" ht="30" customHeight="1">
+      <c r="B76" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="83"/>
-      <c r="D75" s="84"/>
-      <c r="E75" s="84"/>
-      <c r="F75" s="84"/>
-      <c r="G75" s="84"/>
-    </row>
-    <row r="76" spans="2:7" ht="30" customHeight="1">
-      <c r="B76" s="15" t="s">
+      <c r="C76" s="63"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="69"/>
-      <c r="D76" s="69"/>
-      <c r="E76" s="85" t="s">
+      <c r="F76" s="80"/>
+      <c r="G76" s="81"/>
+    </row>
+    <row r="77" spans="2:7" ht="30" customHeight="1">
+      <c r="B77" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F76" s="86"/>
-      <c r="G76" s="87"/>
-    </row>
-    <row r="77" spans="2:7" ht="30" customHeight="1">
-      <c r="B77" s="16" t="s">
+      <c r="C77" s="63"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" s="65"/>
+      <c r="G77" s="66"/>
+    </row>
+    <row r="78" spans="2:7" ht="30" customHeight="1">
+      <c r="B78" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="63"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F78" s="65"/>
+      <c r="G78" s="66"/>
+    </row>
+    <row r="79" spans="2:7" ht="30" customHeight="1">
+      <c r="B79" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C77" s="69"/>
-      <c r="D77" s="69"/>
-      <c r="E77" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F77" s="71"/>
-      <c r="G77" s="72"/>
-    </row>
-    <row r="78" spans="2:7" ht="30" customHeight="1">
-      <c r="B78" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C78" s="69"/>
-      <c r="D78" s="69"/>
-      <c r="E78" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F78" s="71"/>
-      <c r="G78" s="72"/>
-    </row>
-    <row r="79" spans="2:7" ht="30" customHeight="1">
-      <c r="B79" s="16" t="s">
+      <c r="C79" s="63"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" s="65"/>
+      <c r="G79" s="66"/>
+    </row>
+    <row r="80" spans="2:7" ht="30" customHeight="1">
+      <c r="B80" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="69"/>
-      <c r="D79" s="69"/>
-      <c r="E79" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F79" s="71"/>
-      <c r="G79" s="72"/>
-    </row>
-    <row r="80" spans="2:7" ht="30" customHeight="1">
-      <c r="B80" s="16" t="s">
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" s="65"/>
+      <c r="G80" s="66"/>
+    </row>
+    <row r="81" spans="2:7" ht="30" customHeight="1">
+      <c r="B81" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C80" s="69"/>
-      <c r="D80" s="69"/>
-      <c r="E80" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F80" s="71"/>
-      <c r="G80" s="72"/>
-    </row>
-    <row r="81" spans="2:7" ht="30" customHeight="1">
-      <c r="B81" s="16" t="s">
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" s="65"/>
+      <c r="G81" s="66"/>
+    </row>
+    <row r="82" spans="2:7" ht="30" customHeight="1">
+      <c r="B82" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C81" s="69"/>
-      <c r="D81" s="69"/>
-      <c r="E81" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F81" s="71"/>
-      <c r="G81" s="72"/>
-    </row>
-    <row r="82" spans="2:7" ht="30" customHeight="1">
-      <c r="B82" s="16" t="s">
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F82" s="65"/>
+      <c r="G82" s="66"/>
+    </row>
+    <row r="83" spans="2:7" ht="30" customHeight="1">
+      <c r="B83" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="69"/>
-      <c r="D82" s="69"/>
-      <c r="E82" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F82" s="71"/>
-      <c r="G82" s="72"/>
-    </row>
-    <row r="83" spans="2:7" ht="30" customHeight="1">
-      <c r="B83" s="16" t="s">
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" s="65"/>
+      <c r="G83" s="66"/>
+    </row>
+    <row r="84" spans="2:7" ht="30" customHeight="1">
+      <c r="B84" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C83" s="69"/>
-      <c r="D83" s="69"/>
-      <c r="E83" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F83" s="71"/>
-      <c r="G83" s="72"/>
-    </row>
-    <row r="84" spans="2:7" ht="30" customHeight="1">
-      <c r="B84" s="16" t="s">
+      <c r="C84" s="63"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F84" s="65"/>
+      <c r="G84" s="66"/>
+    </row>
+    <row r="85" spans="2:7" ht="30" customHeight="1">
+      <c r="B85" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C84" s="69"/>
-      <c r="D84" s="69"/>
-      <c r="E84" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F84" s="71"/>
-      <c r="G84" s="72"/>
-    </row>
-    <row r="85" spans="2:7" ht="30" customHeight="1">
-      <c r="B85" s="16" t="s">
+      <c r="C85" s="82"/>
+      <c r="D85" s="83"/>
+      <c r="E85" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F85" s="65"/>
+      <c r="G85" s="66"/>
+    </row>
+    <row r="86" spans="2:7" ht="30" customHeight="1">
+      <c r="B86" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="88"/>
-      <c r="D85" s="89"/>
-      <c r="E85" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F85" s="71"/>
-      <c r="G85" s="72"/>
-    </row>
-    <row r="86" spans="2:7" ht="30" customHeight="1">
-      <c r="B86" s="16" t="s">
+      <c r="C86" s="82"/>
+      <c r="D86" s="83"/>
+      <c r="E86" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" s="65"/>
+      <c r="G86" s="66"/>
+    </row>
+    <row r="87" spans="2:7" ht="30" customHeight="1">
+      <c r="B87" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C86" s="88"/>
-      <c r="D86" s="89"/>
-      <c r="E86" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F86" s="71"/>
-      <c r="G86" s="72"/>
-    </row>
-    <row r="87" spans="2:7" ht="30" customHeight="1">
-      <c r="B87" s="16" t="s">
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" s="65"/>
+      <c r="G87" s="66"/>
+    </row>
+    <row r="88" spans="2:7" ht="30" customHeight="1">
+      <c r="B88" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" s="83"/>
+      <c r="D88" s="99"/>
+      <c r="E88" s="99"/>
+      <c r="F88" s="99"/>
+      <c r="G88" s="100"/>
+    </row>
+    <row r="89" spans="2:7" ht="30" customHeight="1" thickBot="1">
+      <c r="B89" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C87" s="69"/>
-      <c r="D87" s="69"/>
-      <c r="E87" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F87" s="71"/>
-      <c r="G87" s="72"/>
-    </row>
-    <row r="88" spans="2:7" ht="30" customHeight="1">
-      <c r="B88" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C88" s="89"/>
-      <c r="D88" s="105"/>
-      <c r="E88" s="105"/>
-      <c r="F88" s="105"/>
-      <c r="G88" s="106"/>
-    </row>
-    <row r="89" spans="2:7" ht="30" customHeight="1" thickBot="1">
-      <c r="B89" s="17" t="s">
+      <c r="C89" s="101"/>
+      <c r="D89" s="102"/>
+      <c r="E89" s="102"/>
+      <c r="F89" s="102"/>
+      <c r="G89" s="103"/>
+    </row>
+    <row r="90" spans="2:7" ht="30" customHeight="1">
+      <c r="B90" s="104" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="105"/>
+      <c r="D90" s="105"/>
+      <c r="E90" s="105"/>
+      <c r="F90" s="105"/>
+      <c r="G90" s="106"/>
+    </row>
+    <row r="91" spans="2:7" ht="30" customHeight="1">
+      <c r="B91" s="107"/>
+      <c r="C91" s="108"/>
+      <c r="D91" s="108"/>
+      <c r="E91" s="108"/>
+      <c r="F91" s="108"/>
+      <c r="G91" s="109"/>
+    </row>
+    <row r="92" spans="2:7" ht="30" customHeight="1" thickBot="1">
+      <c r="B92" s="110"/>
+      <c r="C92" s="111"/>
+      <c r="D92" s="111"/>
+      <c r="E92" s="111"/>
+      <c r="F92" s="111"/>
+      <c r="G92" s="112"/>
+    </row>
+    <row r="93" spans="2:7">
+      <c r="B93" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="C89" s="107"/>
-      <c r="D89" s="108"/>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="109"/>
-    </row>
-    <row r="90" spans="2:7" ht="30" customHeight="1">
-      <c r="B90" s="110" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90" s="111"/>
-      <c r="D90" s="111"/>
-      <c r="E90" s="111"/>
-      <c r="F90" s="111"/>
-      <c r="G90" s="112"/>
-    </row>
-    <row r="91" spans="2:7" ht="30" customHeight="1">
-      <c r="B91" s="113"/>
-      <c r="C91" s="114"/>
-      <c r="D91" s="114"/>
-      <c r="E91" s="114"/>
-      <c r="F91" s="114"/>
-      <c r="G91" s="115"/>
-    </row>
-    <row r="92" spans="2:7" ht="30" customHeight="1" thickBot="1">
-      <c r="B92" s="116"/>
-      <c r="C92" s="117"/>
-      <c r="D92" s="117"/>
-      <c r="E92" s="117"/>
-      <c r="F92" s="117"/>
-      <c r="G92" s="118"/>
-    </row>
-    <row r="93" spans="2:7">
-      <c r="B93" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="C93" s="91"/>
-      <c r="D93" s="92"/>
-      <c r="E93" s="99"/>
-      <c r="F93" s="99"/>
-      <c r="G93" s="100"/>
+      <c r="C93" s="85"/>
+      <c r="D93" s="86"/>
+      <c r="E93" s="93"/>
+      <c r="F93" s="93"/>
+      <c r="G93" s="94"/>
     </row>
     <row r="94" spans="2:7">
-      <c r="B94" s="93"/>
-      <c r="C94" s="94"/>
-      <c r="D94" s="95"/>
-      <c r="E94" s="101"/>
-      <c r="F94" s="101"/>
-      <c r="G94" s="102"/>
+      <c r="B94" s="87"/>
+      <c r="C94" s="88"/>
+      <c r="D94" s="89"/>
+      <c r="E94" s="95"/>
+      <c r="F94" s="95"/>
+      <c r="G94" s="96"/>
     </row>
     <row r="95" spans="2:7" ht="39.6" customHeight="1" thickBot="1">
-      <c r="B95" s="96"/>
-      <c r="C95" s="97"/>
-      <c r="D95" s="98"/>
-      <c r="E95" s="103"/>
-      <c r="F95" s="103"/>
-      <c r="G95" s="104"/>
+      <c r="B95" s="90"/>
+      <c r="C95" s="91"/>
+      <c r="D95" s="92"/>
+      <c r="E95" s="97"/>
+      <c r="F95" s="97"/>
+      <c r="G95" s="98"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -3636,19 +3622,10 @@
     <mergeCell ref="B55:C59"/>
     <mergeCell ref="D55:D59"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G13 D15:D74" xr:uid="{508A4757-596D-473F-858B-A5C02905DC2F}">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{01645B9D-795D-47FD-9A1E-A227BBD1E6A1}">
       <formula1>44927</formula1>
       <formula2>46387</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9" xr:uid="{FC9C4E5A-8A53-49E1-8C29-1B8733681132}">
-      <formula1>"Komatsu PC200-8MO, Komatsu PC210-10MO, Caterpillar  966H1, Caterpillar 966H2, Doosan DL320A "</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{A8112637-6DAF-486A-ADE0-A0BC0437FB91}">
-      <formula1>"Eider Melendez, Gualberto Albor, Wilfredo Ramirez"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D75:G75" xr:uid="{59E242F2-71F6-4C1F-8338-0EBA0839EA3D}">
       <formula1>"Si, N/A"</formula1>
